--- a/louvers/files/reference_xls/price_xls/aerofoil_af400.xlsx
+++ b/louvers/files/reference_xls/price_xls/aerofoil_af400.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C73930-62AF-9D45-90E1-058B87B87299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019B3200-17EA-D948-A0B5-A18DD92B858E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
   </bookViews>
@@ -979,39 +979,39 @@
       </c>
       <c r="B2" s="10">
         <f>C2/10.76391</f>
-        <v>622.56652090179125</v>
+        <v>684.82317299197041</v>
       </c>
       <c r="C2" s="11">
         <f>((1000/B7)*3.574)*A7</f>
-        <v>6701.2499999999991</v>
+        <v>7371.3749999999991</v>
       </c>
       <c r="D2" s="12">
         <f>+A7*(1.787*2)</f>
-        <v>2680.5</v>
+        <v>2948.5499999999997</v>
       </c>
       <c r="E2" s="19">
         <f>F2/10.76391</f>
-        <v>680.70629059282362</v>
+        <v>742.96294268300267</v>
       </c>
       <c r="F2" s="20">
         <f>C2+((((646*0.03937)*39.37)*(1000/B7))*0.25)</f>
-        <v>7327.0612483749992</v>
+        <v>7997.1862483749992</v>
       </c>
       <c r="G2" s="21">
         <f>+D2+((((323*2)/25.4)*39.37008)*0.25)</f>
-        <v>2930.8255086614172</v>
+        <v>3198.8755086614169</v>
       </c>
       <c r="H2" s="28">
         <f>I2/10.76391</f>
-        <v>785.35787603668177</v>
+        <v>847.61452812686093</v>
       </c>
       <c r="I2" s="29">
         <f>C2+((((646*0.03937)*39.37)*(1000/B7))*0.7)</f>
-        <v>8453.5214954499988</v>
+        <v>9123.6464954499988</v>
       </c>
       <c r="J2" s="30">
         <f>+G2+((((323*2)/25.4)*39.37008)*0.6)</f>
-        <v>3531.6067294488189</v>
+        <v>3799.6567294488186</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1020,39 +1020,39 @@
       </c>
       <c r="B3" s="37">
         <f>C3/10.76391</f>
-        <v>286.72201830004155</v>
+        <v>315.39422013004571</v>
       </c>
       <c r="C3" s="38">
         <f>((1000/B7)*1.646)*A7</f>
-        <v>3086.25</v>
+        <v>3394.875</v>
       </c>
       <c r="D3" s="39">
         <f>+A7*1.646</f>
-        <v>1234.5</v>
+        <v>1357.9499999999998</v>
       </c>
       <c r="E3" s="34">
         <f>F3/10.76391</f>
-        <v>303.19195305771791</v>
+        <v>331.86415488772207</v>
       </c>
       <c r="F3" s="35">
         <f>C3+((((183*0.03937)*39.37)*(1000/B7))*0.25)</f>
-        <v>3263.5308954375</v>
+        <v>3572.1558954375</v>
       </c>
       <c r="G3" s="36">
         <f>+D3+(((183/25.4)*39.37008)*0.25)</f>
-        <v>1305.4126440944883</v>
+        <v>1428.8626440944881</v>
       </c>
       <c r="H3" s="40">
         <f>I3/10.76391</f>
-        <v>332.83783562153531</v>
+        <v>361.51003745153946</v>
       </c>
       <c r="I3" s="41">
         <f>C3+((((183*0.03937)*39.37)*(1000/B7))*0.7)</f>
-        <v>3582.6365072250001</v>
+        <v>3891.2615072250001</v>
       </c>
       <c r="J3" s="42">
         <f>+G3+(((183/25.4)*39.37008)*0.6)</f>
-        <v>1475.6029899212599</v>
+        <v>1599.0529899212597</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="6" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -1061,29 +1061,29 @@
       </c>
       <c r="B4" s="13">
         <f>SUM(B2:B3)</f>
-        <v>909.2885392018328</v>
+        <v>1000.2173931220161</v>
       </c>
       <c r="C4" s="14">
         <f>SUM(C2:C3)</f>
-        <v>9787.5</v>
+        <v>10766.25</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="22">
         <f>SUM(E2:E3)</f>
-        <v>983.89824365054153</v>
+        <v>1074.8270975707246</v>
       </c>
       <c r="F4" s="23">
         <f>SUM(F2:F3)</f>
-        <v>10590.592143812499</v>
+        <v>11569.342143812499</v>
       </c>
       <c r="G4" s="24"/>
       <c r="H4" s="31">
         <f>SUM(H2:H3)</f>
-        <v>1118.1957116582171</v>
+        <v>1209.1245655784005</v>
       </c>
       <c r="I4" s="32">
         <f>SUM(I2:I3)</f>
-        <v>12036.158002674998</v>
+        <v>13014.908002674998</v>
       </c>
       <c r="J4" s="33"/>
     </row>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="7" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="B7" s="5">
         <v>400</v>
